--- a/QCM7_3_MATH.xlsx
+++ b/QCM7_3_MATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4205215C-8B6E-4B02-8B22-410BE7928BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A42964F-4ACE-4E30-B15B-CE675F9F170A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -162,13 +162,13 @@
     <t>$\frac{1}{8}(\sin 3 \theta+3 \sin \theta)$</t>
   </si>
   <si>
-    <t>Calculer :$ \left( \int_{1}^{e} t\ln(t)dt$ ;$ \int_{1}^{e} \frac{\ln(t)}{t^2}dt$ ; $\int_{1}^{e^2} \sqrt{t}\ln(t)dt \right)$</t>
-  </si>
-  <si>
     <t>$\int_{-\frac{\pi}{6}}^{\frac{\pi}{6}} \sin^7(t) dt$</t>
   </si>
   <si>
     <t>$\int_{\ln 2}^{\ln 3} \frac{e^t+e^{-t}}{e^t-e^{-t}} dt$</t>
+  </si>
+  <si>
+    <t>Calculer :$\left( \int_{1}^{e} t\ln(t)dt ; \int_{1}^{e} \frac{\ln(t)}{t^2}dt ; \int_{1}^{e^2} \sqrt{t}\ln(t)dt \right)$</t>
   </si>
 </sst>
 </file>
@@ -684,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>23</v>
@@ -710,7 +710,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>26</v>
@@ -736,7 +736,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>28</v>

--- a/QCM7_3_MATH.xlsx
+++ b/QCM7_3_MATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A42964F-4ACE-4E30-B15B-CE675F9F170A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604F28FD-E3D9-4A0C-856E-346211B0FD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,7 +608,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" customWidth="1"/>
     <col min="4" max="7" width="35" customWidth="1"/>
     <col min="8" max="9" width="33.140625" customWidth="1"/>
@@ -651,8 +651,8 @@
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>19</v>
+      <c r="B2" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -677,8 +677,8 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>23</v>
+      <c r="B3" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -703,8 +703,8 @@
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>26</v>
+      <c r="B4" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -729,8 +729,8 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>28</v>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -755,8 +755,8 @@
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>18</v>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -781,8 +781,8 @@
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -807,8 +807,8 @@
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>34</v>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -833,8 +833,8 @@
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>36</v>
+      <c r="B9" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -859,8 +859,8 @@
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>39</v>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -885,8 +885,8 @@
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>42</v>
+      <c r="B11" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
